--- a/public/plantilla-control-hidrocarburos.xlsx
+++ b/public/plantilla-control-hidrocarburos.xlsx
@@ -510,7 +510,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -549,7 +549,7 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -712,6 +712,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="20" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3008,7 +3011,7 @@
       <c r="A17" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="16" t="n"/>
+      <c r="B17" s="79" t="n"/>
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="20" t="n"/>
       <c r="E17" s="48" t="n"/>
@@ -3024,7 +3027,7 @@
       <c r="A18" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="79" t="n"/>
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="20" t="n"/>
       <c r="E18" s="48" t="n"/>
@@ -3040,7 +3043,7 @@
       <c r="A19" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="16" t="n"/>
+      <c r="B19" s="79" t="n"/>
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="20" t="n"/>
       <c r="E19" s="48" t="n"/>
@@ -3056,7 +3059,7 @@
       <c r="A20" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="16" t="n"/>
+      <c r="B20" s="79" t="n"/>
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="20" t="n"/>
       <c r="E20" s="48" t="n"/>
@@ -3072,7 +3075,7 @@
       <c r="A21" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="79" t="n"/>
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="20" t="n"/>
       <c r="E21" s="48" t="n"/>
@@ -3088,7 +3091,7 @@
       <c r="A22" s="48" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="16" t="n"/>
+      <c r="B22" s="79" t="n"/>
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="20" t="n"/>
       <c r="E22" s="48" t="n"/>
@@ -3104,7 +3107,7 @@
       <c r="A23" s="48" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="16" t="n"/>
+      <c r="B23" s="79" t="n"/>
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="20" t="n"/>
       <c r="E23" s="48" t="n"/>
@@ -3120,7 +3123,7 @@
       <c r="A24" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="16" t="n"/>
+      <c r="B24" s="79" t="n"/>
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="20" t="n"/>
       <c r="E24" s="48" t="n"/>
@@ -3136,7 +3139,7 @@
       <c r="A25" s="48" t="n">
         <v>9</v>
       </c>
-      <c r="B25" s="16" t="n"/>
+      <c r="B25" s="79" t="n"/>
       <c r="C25" s="46" t="n"/>
       <c r="D25" s="20" t="n"/>
       <c r="E25" s="48" t="n"/>
@@ -3152,7 +3155,7 @@
       <c r="A26" s="48" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="16" t="n"/>
+      <c r="B26" s="79" t="n"/>
       <c r="C26" s="46" t="n"/>
       <c r="D26" s="20" t="n"/>
       <c r="E26" s="48" t="n"/>
@@ -3168,7 +3171,7 @@
       <c r="A27" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="B27" s="16" t="n"/>
+      <c r="B27" s="79" t="n"/>
       <c r="C27" s="46" t="n"/>
       <c r="D27" s="20" t="n"/>
       <c r="E27" s="48" t="n"/>
@@ -3184,7 +3187,7 @@
       <c r="A28" s="48" t="n">
         <v>12</v>
       </c>
-      <c r="B28" s="16" t="n"/>
+      <c r="B28" s="79" t="n"/>
       <c r="C28" s="46" t="n"/>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="48" t="n"/>
@@ -3200,7 +3203,7 @@
       <c r="A29" s="48" t="n">
         <v>13</v>
       </c>
-      <c r="B29" s="16" t="n"/>
+      <c r="B29" s="79" t="n"/>
       <c r="C29" s="46" t="n"/>
       <c r="D29" s="20" t="n"/>
       <c r="E29" s="48" t="n"/>
@@ -3216,7 +3219,7 @@
       <c r="A30" s="48" t="n">
         <v>14</v>
       </c>
-      <c r="B30" s="16" t="n"/>
+      <c r="B30" s="79" t="n"/>
       <c r="C30" s="46" t="n"/>
       <c r="D30" s="20" t="n"/>
       <c r="E30" s="48" t="n"/>

--- a/public/plantilla-control-hidrocarburos.xlsx
+++ b/public/plantilla-control-hidrocarburos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="1" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Hidrocarburos" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-control-hidrocarburos.xlsx
+++ b/public/plantilla-control-hidrocarburos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Hidrocarburos" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="17">
+  <numFmts count="0"/>
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,6 +139,10 @@
       <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -510,7 +515,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -712,8 +717,57 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyNumberFormat="1" numFmtId="20" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="20" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2347,6 +2401,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2696,6 +2818,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="33" min="1" max="1"/>
     <col width="13" customWidth="1" style="33" min="2" max="3"/>
+    <col width="13" customWidth="1" style="33" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="33" min="4" max="4"/>
     <col width="10" customWidth="1" style="33" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="33" min="6" max="6"/>
@@ -2862,16 +2985,16 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="C11" s="80" t="n"/>
+      <c r="D11" s="81" t="n"/>
+      <c r="E11" s="81" t="n"/>
+      <c r="F11" s="81" t="n"/>
+      <c r="G11" s="81" t="n"/>
+      <c r="H11" s="81" t="n"/>
+      <c r="I11" s="81" t="n"/>
+      <c r="J11" s="81" t="n"/>
+      <c r="K11" s="81" t="n"/>
+      <c r="L11" s="82" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="33">
       <c r="A12" s="25" t="inlineStr">
@@ -2880,20 +3003,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="80" t="n"/>
+      <c r="D12" s="81" t="n"/>
+      <c r="E12" s="81" t="n"/>
+      <c r="F12" s="81" t="n"/>
+      <c r="G12" s="82" t="n"/>
       <c r="H12" s="25" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="22" t="n"/>
-      <c r="J12" s="31" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="J12" s="80" t="n"/>
+      <c r="K12" s="81" t="n"/>
+      <c r="L12" s="82" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="33">
       <c r="A13" s="25" t="inlineStr">
@@ -2902,24 +3025,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="83" t="n"/>
+      <c r="D13" s="82" t="n"/>
       <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Tanque o punto de suministro</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="22" t="n"/>
+      <c r="G13" s="80" t="n"/>
+      <c r="H13" s="82" t="n"/>
       <c r="I13" s="25" t="inlineStr">
         <is>
           <t>Capacidad (gal)</t>
         </is>
       </c>
       <c r="J13" s="22" t="n"/>
-      <c r="K13" s="44" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="84" t="n"/>
+      <c r="L13" s="82" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="33">
       <c r="A14" s="25" t="inlineStr">
@@ -2928,20 +3051,20 @@
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="22" t="n"/>
+      <c r="C14" s="80" t="n"/>
+      <c r="D14" s="81" t="n"/>
+      <c r="E14" s="81" t="n"/>
+      <c r="F14" s="81" t="n"/>
+      <c r="G14" s="82" t="n"/>
       <c r="H14" s="25" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
       <c r="I14" s="22" t="n"/>
-      <c r="J14" s="31" t="n"/>
-      <c r="K14" s="30" t="n"/>
-      <c r="L14" s="22" t="n"/>
+      <c r="J14" s="80" t="n"/>
+      <c r="K14" s="81" t="n"/>
+      <c r="L14" s="82" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="33">
       <c r="A15" s="35" t="inlineStr">
@@ -3008,228 +3131,228 @@
       <c r="L16" s="28" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1" s="33">
-      <c r="A17" s="48" t="n">
+      <c r="A17" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="79" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="48" t="n"/>
-      <c r="I17" s="46" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="46" t="n"/>
-      <c r="L17" s="20" t="n"/>
+      <c r="B17" s="86" t="n"/>
+      <c r="C17" s="87" t="n"/>
+      <c r="D17" s="88" t="n"/>
+      <c r="E17" s="89" t="n"/>
+      <c r="F17" s="88" t="n"/>
+      <c r="G17" s="89" t="n"/>
+      <c r="H17" s="89" t="n"/>
+      <c r="I17" s="87" t="n"/>
+      <c r="J17" s="88" t="n"/>
+      <c r="K17" s="87" t="n"/>
+      <c r="L17" s="88" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="33">
-      <c r="A18" s="48" t="n">
+      <c r="A18" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="79" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="48" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="48" t="n"/>
-      <c r="H18" s="48" t="n"/>
-      <c r="I18" s="46" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="46" t="n"/>
-      <c r="L18" s="20" t="n"/>
+      <c r="B18" s="86" t="n"/>
+      <c r="C18" s="87" t="n"/>
+      <c r="D18" s="88" t="n"/>
+      <c r="E18" s="89" t="n"/>
+      <c r="F18" s="88" t="n"/>
+      <c r="G18" s="89" t="n"/>
+      <c r="H18" s="89" t="n"/>
+      <c r="I18" s="87" t="n"/>
+      <c r="J18" s="88" t="n"/>
+      <c r="K18" s="87" t="n"/>
+      <c r="L18" s="88" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1" s="33">
-      <c r="A19" s="48" t="n">
+      <c r="A19" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="79" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="48" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="48" t="n"/>
-      <c r="H19" s="48" t="n"/>
-      <c r="I19" s="46" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="46" t="n"/>
-      <c r="L19" s="20" t="n"/>
+      <c r="B19" s="86" t="n"/>
+      <c r="C19" s="87" t="n"/>
+      <c r="D19" s="88" t="n"/>
+      <c r="E19" s="89" t="n"/>
+      <c r="F19" s="88" t="n"/>
+      <c r="G19" s="89" t="n"/>
+      <c r="H19" s="89" t="n"/>
+      <c r="I19" s="87" t="n"/>
+      <c r="J19" s="88" t="n"/>
+      <c r="K19" s="87" t="n"/>
+      <c r="L19" s="88" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1" s="33">
-      <c r="A20" s="48" t="n">
+      <c r="A20" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="79" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="48" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="48" t="n"/>
-      <c r="H20" s="48" t="n"/>
-      <c r="I20" s="46" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="46" t="n"/>
-      <c r="L20" s="20" t="n"/>
+      <c r="B20" s="86" t="n"/>
+      <c r="C20" s="87" t="n"/>
+      <c r="D20" s="88" t="n"/>
+      <c r="E20" s="89" t="n"/>
+      <c r="F20" s="88" t="n"/>
+      <c r="G20" s="89" t="n"/>
+      <c r="H20" s="89" t="n"/>
+      <c r="I20" s="87" t="n"/>
+      <c r="J20" s="88" t="n"/>
+      <c r="K20" s="87" t="n"/>
+      <c r="L20" s="88" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1" s="33">
-      <c r="A21" s="48" t="n">
+      <c r="A21" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="79" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="48" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="48" t="n"/>
-      <c r="H21" s="48" t="n"/>
-      <c r="I21" s="46" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="46" t="n"/>
-      <c r="L21" s="20" t="n"/>
+      <c r="B21" s="86" t="n"/>
+      <c r="C21" s="87" t="n"/>
+      <c r="D21" s="88" t="n"/>
+      <c r="E21" s="89" t="n"/>
+      <c r="F21" s="88" t="n"/>
+      <c r="G21" s="89" t="n"/>
+      <c r="H21" s="89" t="n"/>
+      <c r="I21" s="87" t="n"/>
+      <c r="J21" s="88" t="n"/>
+      <c r="K21" s="87" t="n"/>
+      <c r="L21" s="88" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1" s="33">
-      <c r="A22" s="48" t="n">
+      <c r="A22" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="79" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="48" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="48" t="n"/>
-      <c r="H22" s="48" t="n"/>
-      <c r="I22" s="46" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="46" t="n"/>
-      <c r="L22" s="20" t="n"/>
+      <c r="B22" s="86" t="n"/>
+      <c r="C22" s="87" t="n"/>
+      <c r="D22" s="88" t="n"/>
+      <c r="E22" s="89" t="n"/>
+      <c r="F22" s="88" t="n"/>
+      <c r="G22" s="89" t="n"/>
+      <c r="H22" s="89" t="n"/>
+      <c r="I22" s="87" t="n"/>
+      <c r="J22" s="88" t="n"/>
+      <c r="K22" s="87" t="n"/>
+      <c r="L22" s="88" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1" s="33">
-      <c r="A23" s="48" t="n">
+      <c r="A23" s="85" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="79" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="48" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="48" t="n"/>
-      <c r="H23" s="48" t="n"/>
-      <c r="I23" s="46" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="46" t="n"/>
-      <c r="L23" s="20" t="n"/>
+      <c r="B23" s="86" t="n"/>
+      <c r="C23" s="87" t="n"/>
+      <c r="D23" s="88" t="n"/>
+      <c r="E23" s="89" t="n"/>
+      <c r="F23" s="88" t="n"/>
+      <c r="G23" s="89" t="n"/>
+      <c r="H23" s="89" t="n"/>
+      <c r="I23" s="87" t="n"/>
+      <c r="J23" s="88" t="n"/>
+      <c r="K23" s="87" t="n"/>
+      <c r="L23" s="88" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1" s="33">
-      <c r="A24" s="48" t="n">
+      <c r="A24" s="85" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="79" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="48" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="48" t="n"/>
-      <c r="H24" s="48" t="n"/>
-      <c r="I24" s="46" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="46" t="n"/>
-      <c r="L24" s="20" t="n"/>
+      <c r="B24" s="86" t="n"/>
+      <c r="C24" s="87" t="n"/>
+      <c r="D24" s="88" t="n"/>
+      <c r="E24" s="89" t="n"/>
+      <c r="F24" s="88" t="n"/>
+      <c r="G24" s="89" t="n"/>
+      <c r="H24" s="89" t="n"/>
+      <c r="I24" s="87" t="n"/>
+      <c r="J24" s="88" t="n"/>
+      <c r="K24" s="87" t="n"/>
+      <c r="L24" s="88" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1" s="33">
-      <c r="A25" s="48" t="n">
+      <c r="A25" s="85" t="n">
         <v>9</v>
       </c>
-      <c r="B25" s="79" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="48" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="48" t="n"/>
-      <c r="H25" s="48" t="n"/>
-      <c r="I25" s="46" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="46" t="n"/>
-      <c r="L25" s="20" t="n"/>
+      <c r="B25" s="86" t="n"/>
+      <c r="C25" s="87" t="n"/>
+      <c r="D25" s="88" t="n"/>
+      <c r="E25" s="89" t="n"/>
+      <c r="F25" s="88" t="n"/>
+      <c r="G25" s="89" t="n"/>
+      <c r="H25" s="89" t="n"/>
+      <c r="I25" s="87" t="n"/>
+      <c r="J25" s="88" t="n"/>
+      <c r="K25" s="87" t="n"/>
+      <c r="L25" s="88" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1" s="33">
-      <c r="A26" s="48" t="n">
+      <c r="A26" s="85" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="79" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="48" t="n"/>
-      <c r="F26" s="20" t="n"/>
-      <c r="G26" s="48" t="n"/>
-      <c r="H26" s="48" t="n"/>
-      <c r="I26" s="46" t="n"/>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="46" t="n"/>
-      <c r="L26" s="20" t="n"/>
+      <c r="B26" s="86" t="n"/>
+      <c r="C26" s="87" t="n"/>
+      <c r="D26" s="88" t="n"/>
+      <c r="E26" s="89" t="n"/>
+      <c r="F26" s="88" t="n"/>
+      <c r="G26" s="89" t="n"/>
+      <c r="H26" s="89" t="n"/>
+      <c r="I26" s="87" t="n"/>
+      <c r="J26" s="88" t="n"/>
+      <c r="K26" s="87" t="n"/>
+      <c r="L26" s="88" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1" s="33">
-      <c r="A27" s="48" t="n">
+      <c r="A27" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="B27" s="79" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="48" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="48" t="n"/>
-      <c r="H27" s="48" t="n"/>
-      <c r="I27" s="46" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="46" t="n"/>
-      <c r="L27" s="20" t="n"/>
+      <c r="B27" s="86" t="n"/>
+      <c r="C27" s="87" t="n"/>
+      <c r="D27" s="88" t="n"/>
+      <c r="E27" s="89" t="n"/>
+      <c r="F27" s="88" t="n"/>
+      <c r="G27" s="89" t="n"/>
+      <c r="H27" s="89" t="n"/>
+      <c r="I27" s="87" t="n"/>
+      <c r="J27" s="88" t="n"/>
+      <c r="K27" s="87" t="n"/>
+      <c r="L27" s="88" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1" s="33">
-      <c r="A28" s="48" t="n">
+      <c r="A28" s="85" t="n">
         <v>12</v>
       </c>
-      <c r="B28" s="79" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="48" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="48" t="n"/>
-      <c r="H28" s="48" t="n"/>
-      <c r="I28" s="46" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="46" t="n"/>
-      <c r="L28" s="20" t="n"/>
+      <c r="B28" s="86" t="n"/>
+      <c r="C28" s="87" t="n"/>
+      <c r="D28" s="88" t="n"/>
+      <c r="E28" s="89" t="n"/>
+      <c r="F28" s="88" t="n"/>
+      <c r="G28" s="89" t="n"/>
+      <c r="H28" s="89" t="n"/>
+      <c r="I28" s="87" t="n"/>
+      <c r="J28" s="88" t="n"/>
+      <c r="K28" s="87" t="n"/>
+      <c r="L28" s="88" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1" s="33">
-      <c r="A29" s="48" t="n">
+      <c r="A29" s="85" t="n">
         <v>13</v>
       </c>
-      <c r="B29" s="79" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="48" t="n"/>
-      <c r="F29" s="20" t="n"/>
-      <c r="G29" s="48" t="n"/>
-      <c r="H29" s="48" t="n"/>
-      <c r="I29" s="46" t="n"/>
-      <c r="J29" s="20" t="n"/>
-      <c r="K29" s="46" t="n"/>
-      <c r="L29" s="20" t="n"/>
+      <c r="B29" s="86" t="n"/>
+      <c r="C29" s="87" t="n"/>
+      <c r="D29" s="88" t="n"/>
+      <c r="E29" s="89" t="n"/>
+      <c r="F29" s="88" t="n"/>
+      <c r="G29" s="89" t="n"/>
+      <c r="H29" s="89" t="n"/>
+      <c r="I29" s="87" t="n"/>
+      <c r="J29" s="88" t="n"/>
+      <c r="K29" s="87" t="n"/>
+      <c r="L29" s="88" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1" s="33">
-      <c r="A30" s="48" t="n">
+      <c r="A30" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="B30" s="79" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="48" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="48" t="n"/>
-      <c r="H30" s="48" t="n"/>
-      <c r="I30" s="46" t="n"/>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="46" t="n"/>
-      <c r="L30" s="20" t="n"/>
+      <c r="B30" s="86" t="n"/>
+      <c r="C30" s="87" t="n"/>
+      <c r="D30" s="88" t="n"/>
+      <c r="E30" s="89" t="n"/>
+      <c r="F30" s="88" t="n"/>
+      <c r="G30" s="89" t="n"/>
+      <c r="H30" s="89" t="n"/>
+      <c r="I30" s="87" t="n"/>
+      <c r="J30" s="88" t="n"/>
+      <c r="K30" s="87" t="n"/>
+      <c r="L30" s="88" t="n"/>
     </row>
     <row r="31" ht="19.95" customHeight="1" s="33">
       <c r="A31" s="51" t="inlineStr">
@@ -3246,11 +3369,11 @@
         <f>SUM(G17:G30)</f>
         <v/>
       </c>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="30" t="n"/>
-      <c r="J31" s="30" t="n"/>
-      <c r="K31" s="30" t="n"/>
-      <c r="L31" s="22" t="n"/>
+      <c r="H31" s="80" t="n"/>
+      <c r="I31" s="81" t="n"/>
+      <c r="J31" s="81" t="n"/>
+      <c r="K31" s="81" t="n"/>
+      <c r="L31" s="82" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="33">
       <c r="A32" s="35" t="inlineStr">
@@ -3277,23 +3400,23 @@
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
-      <c r="C33" s="44" t="n"/>
-      <c r="D33" s="22" t="n"/>
+      <c r="C33" s="84" t="n"/>
+      <c r="D33" s="82" t="n"/>
       <c r="E33" s="25" t="inlineStr">
         <is>
           <t>Recibido hoy (gal)</t>
         </is>
       </c>
       <c r="F33" s="22" t="n"/>
-      <c r="G33" s="44" t="n"/>
-      <c r="H33" s="22" t="n"/>
+      <c r="G33" s="84" t="n"/>
+      <c r="H33" s="82" t="n"/>
       <c r="I33" s="25" t="inlineStr">
         <is>
           <t>Despachado hoy (gal)</t>
         </is>
       </c>
       <c r="J33" s="22" t="n"/>
-      <c r="K33" s="44">
+      <c r="K33" s="90">
         <f>G31</f>
         <v/>
       </c>
@@ -3306,7 +3429,7 @@
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
-      <c r="C34" s="44">
+      <c r="C34" s="90">
         <f>IF(C33="","",C33+N(G33)-K33)</f>
         <v/>
       </c>
@@ -3317,15 +3440,15 @@
         </is>
       </c>
       <c r="F34" s="22" t="n"/>
-      <c r="G34" s="44" t="n"/>
-      <c r="H34" s="22" t="n"/>
+      <c r="G34" s="84" t="n"/>
+      <c r="H34" s="82" t="n"/>
       <c r="I34" s="25" t="inlineStr">
         <is>
           <t>Diferencia (gal)</t>
         </is>
       </c>
       <c r="J34" s="22" t="n"/>
-      <c r="K34" s="44">
+      <c r="K34" s="90">
         <f>IF(OR(C34="",G34=""),"",G34-C34)</f>
         <v/>
       </c>
@@ -3368,7 +3491,7 @@
       <c r="L36" s="20" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1" s="33">
-      <c r="A37" s="46" t="inlineStr">
+      <c r="A37" s="91" t="inlineStr">
         <is>
           <t>☐ Se suministró sobre piso protegido o con bandeja</t>
         </is>
@@ -3378,7 +3501,7 @@
       <c r="D37" s="24" t="n"/>
       <c r="E37" s="24" t="n"/>
       <c r="F37" s="20" t="n"/>
-      <c r="G37" s="46" t="inlineStr">
+      <c r="G37" s="91" t="inlineStr">
         <is>
           <t>☐ Kit antiderrames disponible y completo</t>
         </is>
@@ -3390,7 +3513,7 @@
       <c r="L37" s="20" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="33">
-      <c r="A38" s="46" t="inlineStr">
+      <c r="A38" s="91" t="inlineStr">
         <is>
           <t>☐ Sin derrames ni goteos en la zona</t>
         </is>
@@ -3400,7 +3523,7 @@
       <c r="D38" s="24" t="n"/>
       <c r="E38" s="24" t="n"/>
       <c r="F38" s="20" t="n"/>
-      <c r="G38" s="46" t="inlineStr">
+      <c r="G38" s="91" t="inlineStr">
         <is>
           <t>☐ Tanque o cancha con contención en buen estado</t>
         </is>
@@ -3412,7 +3535,7 @@
       <c r="L38" s="20" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="33">
-      <c r="A39" s="46" t="inlineStr">
+      <c r="A39" s="91" t="inlineStr">
         <is>
           <t>☐ Zona señalizada, sin fuentes de ignición</t>
         </is>
@@ -3422,7 +3545,7 @@
       <c r="D39" s="24" t="n"/>
       <c r="E39" s="24" t="n"/>
       <c r="F39" s="20" t="n"/>
-      <c r="G39" s="46" t="inlineStr">
+      <c r="G39" s="91" t="inlineStr">
         <is>
           <t>☐ Extintor vigente y a la mano</t>
         </is>
@@ -3434,7 +3557,7 @@
       <c r="L39" s="20" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="33">
-      <c r="A40" s="46" t="inlineStr">
+      <c r="A40" s="91" t="inlineStr">
         <is>
           <t>☐ Entradas y salidas registradas en este formato</t>
         </is>
@@ -3444,7 +3567,7 @@
       <c r="D40" s="24" t="n"/>
       <c r="E40" s="24" t="n"/>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="46" t="inlineStr">
+      <c r="G40" s="91" t="inlineStr">
         <is>
           <t>☐ Se presentó un derrame (diligenciar el Incidente Ambiental)</t>
         </is>
@@ -3462,16 +3585,16 @@
         </is>
       </c>
       <c r="B41" s="22" t="n"/>
-      <c r="C41" s="50" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="30" t="n"/>
-      <c r="G41" s="30" t="n"/>
-      <c r="H41" s="30" t="n"/>
-      <c r="I41" s="30" t="n"/>
-      <c r="J41" s="30" t="n"/>
-      <c r="K41" s="30" t="n"/>
-      <c r="L41" s="22" t="n"/>
+      <c r="C41" s="92" t="n"/>
+      <c r="D41" s="81" t="n"/>
+      <c r="E41" s="81" t="n"/>
+      <c r="F41" s="81" t="n"/>
+      <c r="G41" s="81" t="n"/>
+      <c r="H41" s="81" t="n"/>
+      <c r="I41" s="81" t="n"/>
+      <c r="J41" s="81" t="n"/>
+      <c r="K41" s="81" t="n"/>
+      <c r="L41" s="82" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="33">
       <c r="A42" s="35" t="inlineStr">
@@ -3520,20 +3643,20 @@
         </is>
       </c>
       <c r="B44" s="20" t="n"/>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
-      <c r="E44" s="24" t="n"/>
-      <c r="F44" s="20" t="n"/>
+      <c r="C44" s="87" t="n"/>
+      <c r="D44" s="93" t="n"/>
+      <c r="E44" s="93" t="n"/>
+      <c r="F44" s="88" t="n"/>
       <c r="G44" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="H44" s="20" t="n"/>
-      <c r="I44" s="23" t="n"/>
-      <c r="J44" s="24" t="n"/>
-      <c r="K44" s="24" t="n"/>
-      <c r="L44" s="20" t="n"/>
+      <c r="I44" s="87" t="n"/>
+      <c r="J44" s="93" t="n"/>
+      <c r="K44" s="93" t="n"/>
+      <c r="L44" s="88" t="n"/>
     </row>
     <row r="45" ht="21" customHeight="1" s="33">
       <c r="A45" s="19" t="inlineStr">
@@ -3542,20 +3665,20 @@
         </is>
       </c>
       <c r="B45" s="20" t="n"/>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
-      <c r="E45" s="24" t="n"/>
-      <c r="F45" s="20" t="n"/>
+      <c r="C45" s="87" t="n"/>
+      <c r="D45" s="93" t="n"/>
+      <c r="E45" s="93" t="n"/>
+      <c r="F45" s="88" t="n"/>
       <c r="G45" s="19" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="H45" s="20" t="n"/>
-      <c r="I45" s="23" t="n"/>
-      <c r="J45" s="24" t="n"/>
-      <c r="K45" s="24" t="n"/>
-      <c r="L45" s="20" t="n"/>
+      <c r="I45" s="87" t="n"/>
+      <c r="J45" s="93" t="n"/>
+      <c r="K45" s="93" t="n"/>
+      <c r="L45" s="88" t="n"/>
     </row>
     <row r="46" ht="21" customHeight="1" s="33">
       <c r="A46" s="19" t="inlineStr">
@@ -3564,20 +3687,20 @@
         </is>
       </c>
       <c r="B46" s="20" t="n"/>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
-      <c r="E46" s="24" t="n"/>
-      <c r="F46" s="20" t="n"/>
+      <c r="C46" s="87" t="n"/>
+      <c r="D46" s="93" t="n"/>
+      <c r="E46" s="93" t="n"/>
+      <c r="F46" s="88" t="n"/>
       <c r="G46" s="19" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="H46" s="20" t="n"/>
-      <c r="I46" s="23" t="n"/>
-      <c r="J46" s="24" t="n"/>
-      <c r="K46" s="24" t="n"/>
-      <c r="L46" s="20" t="n"/>
+      <c r="I46" s="87" t="n"/>
+      <c r="J46" s="93" t="n"/>
+      <c r="K46" s="93" t="n"/>
+      <c r="L46" s="88" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3591,6 +3714,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="131">
     <mergeCell ref="K24:L24"/>
     <mergeCell ref="K33:L33"/>
